--- a/docs/MIDI_menuItems.xlsx
+++ b/docs/MIDI_menuItems.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="188">
   <si>
     <t>Index #</t>
   </si>
@@ -571,7 +571,19 @@
     <t>setBtnMode</t>
   </si>
   <si>
-    <t>Swell Ena/CC</t>
+    <t>m_footsw1</t>
+  </si>
+  <si>
+    <t>m_footsw2</t>
+  </si>
+  <si>
+    <t>FootSw 1 CC</t>
+  </si>
+  <si>
+    <t>FootSw 2 CC</t>
+  </si>
+  <si>
+    <t>Swell CC</t>
   </si>
 </sst>
 </file>
@@ -1404,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="3" customWidth="1"/>
@@ -1520,7 +1532,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <f t="shared" ref="A3:A54" si="1">A2+1</f>
+        <f t="shared" ref="A3:A56" si="1">A2+1</f>
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1546,23 +1558,23 @@
         <v>96</v>
       </c>
       <c r="I3" s="43" t="str">
-        <f t="shared" ref="I3:I54" si="2">CONCATENATE("""",B3,""", ")</f>
+        <f t="shared" ref="I3:I56" si="2">CONCATENATE("""",B3,""", ")</f>
         <v xml:space="preserve">"Lower Channel", </v>
       </c>
       <c r="J3" s="44" t="str">
-        <f t="shared" ref="J3:J54" si="3">IF(G3="NULL",CONCATENATE(G3,", "),CONCATENATE("&amp;",G3,", "))</f>
+        <f t="shared" ref="J3:J56" si="3">IF(G3="NULL",CONCATENATE(G3,", "),CONCATENATE("&amp;",G3,", "))</f>
         <v xml:space="preserve">&amp;MenuValues[1], </v>
       </c>
       <c r="K3" s="44" t="str">
-        <f t="shared" ref="K3:K54" si="4">IF(H3="NULL",CONCATENATE(H3,", "),CONCATENATE("&amp;",H3,", "))</f>
+        <f t="shared" ref="K3:K56" si="4">IF(H3="NULL",CONCATENATE(H3,", "),CONCATENATE("&amp;",H3,", "))</f>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="L3" s="40" t="str">
-        <f t="shared" ref="L3:L34" si="5">CONCATENATE("  {",I3,C3,", ",J3,K3,D3,", ",E3,"},")</f>
+        <f t="shared" ref="L3:L36" si="5">CONCATENATE("  {",I3,C3,", ",J3,K3,D3,", ",E3,"},")</f>
         <v xml:space="preserve">  {"Lower Channel", m_lower_ch, &amp;MenuValues[1], NULL, 1, 16},</v>
       </c>
       <c r="M3" s="76" t="str">
-        <f t="shared" ref="M3:M54" si="6" xml:space="preserve"> CONCATENATE("  ",F3,",  // ",B3)</f>
+        <f t="shared" ref="M3:M56" si="6" xml:space="preserve"> CONCATENATE("  ",F3,",  // ",B3)</f>
         <v xml:space="preserve">  2,  // Lower Channel</v>
       </c>
       <c r="N3" s="53" t="str">
@@ -1628,7 +1640,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C5" s="20" t="s">
         <v>152</v>
@@ -1651,7 +1663,7 @@
       </c>
       <c r="I5" s="43" t="str">
         <f t="shared" ref="I5" si="8">CONCATENATE("""",B5,""", ")</f>
-        <v xml:space="preserve">"Swell Ena/CC", </v>
+        <v xml:space="preserve">"Swell CC", </v>
       </c>
       <c r="J5" s="44" t="str">
         <f t="shared" ref="J5" si="9">IF(G5="NULL",CONCATENATE(G5,", "),CONCATENATE("&amp;",G5,", "))</f>
@@ -1663,11 +1675,11 @@
       </c>
       <c r="L5" s="40" t="str">
         <f t="shared" ref="L5" si="11">CONCATENATE("  {",I5,C5,", ",J5,K5,D5,", ",E5,"},")</f>
-        <v xml:space="preserve">  {"Swell Ena/CC", m_swell, &amp;MenuValues[3], NULL, -1, 127},</v>
+        <v xml:space="preserve">  {"Swell CC", m_swell, &amp;MenuValues[3], NULL, -1, 127},</v>
       </c>
       <c r="M5" s="76" t="str">
         <f t="shared" ref="M5" si="12" xml:space="preserve"> CONCATENATE("  ",F5,",  // ",B5)</f>
-        <v xml:space="preserve">  -1,  // Swell Ena/CC</v>
+        <v xml:space="preserve">  -1,  // Swell CC</v>
       </c>
       <c r="N5" s="53" t="str">
         <f t="shared" si="7"/>
@@ -1722,362 +1734,367 @@
         <v xml:space="preserve">  -1,  // Pitchwheel Pot</v>
       </c>
       <c r="N6" s="53" t="str">
-        <f>CONCATENATE("  ",C6,",")</f>
+        <f t="shared" ref="N6:N13" si="13">CONCATENATE("  ",C6,",")</f>
         <v xml:space="preserve">  m_pitchwheel,</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="21">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="20">
+        <v>-1</v>
+      </c>
+      <c r="E7" s="20">
+        <v>127</v>
+      </c>
+      <c r="F7" s="20">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="29" t="str">
+        <f t="shared" ref="G7:G8" si="14">CONCATENATE("MenuValues[",A7,"]")</f>
+        <v>MenuValues[5]</v>
+      </c>
+      <c r="H7" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="I7" s="43" t="str">
+        <f t="shared" ref="I7:I8" si="15">CONCATENATE("""",B7,""", ")</f>
+        <v xml:space="preserve">"FootSw 1 CC", </v>
+      </c>
+      <c r="J7" s="44" t="str">
+        <f t="shared" ref="J7:J8" si="16">IF(G7="NULL",CONCATENATE(G7,", "),CONCATENATE("&amp;",G7,", "))</f>
+        <v xml:space="preserve">&amp;MenuValues[5], </v>
+      </c>
+      <c r="K7" s="44" t="str">
+        <f t="shared" ref="K7:K8" si="17">IF(H7="NULL",CONCATENATE(H7,", "),CONCATENATE("&amp;",H7,", "))</f>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="L7" s="40" t="str">
+        <f t="shared" ref="L7:L8" si="18">CONCATENATE("  {",I7,C7,", ",J7,K7,D7,", ",E7,"},")</f>
+        <v xml:space="preserve">  {"FootSw 1 CC", m_footsw1, &amp;MenuValues[5], NULL, -1, 127},</v>
+      </c>
+      <c r="M7" s="76" t="str">
+        <f t="shared" ref="M7:M8" si="19" xml:space="preserve"> CONCATENATE("  ",F7,",  // ",B7)</f>
+        <v xml:space="preserve">  -1,  // FootSw 1 CC</v>
+      </c>
+      <c r="N7" s="53" t="str">
+        <f t="shared" ref="N7:N8" si="20">CONCATENATE("  ",C7,",")</f>
+        <v xml:space="preserve">  m_footsw1,</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="20">
+        <v>-1</v>
+      </c>
+      <c r="E8" s="20">
+        <v>127</v>
+      </c>
+      <c r="F8" s="20">
+        <v>-1</v>
+      </c>
+      <c r="G8" s="29" t="str">
+        <f t="shared" si="14"/>
+        <v>MenuValues[6]</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" s="43" t="str">
+        <f t="shared" si="15"/>
+        <v xml:space="preserve">"FootSw 2 CC", </v>
+      </c>
+      <c r="J8" s="44" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">&amp;MenuValues[6], </v>
+      </c>
+      <c r="K8" s="44" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="L8" s="40" t="str">
+        <f t="shared" si="18"/>
+        <v xml:space="preserve">  {"FootSw 2 CC", m_footsw2, &amp;MenuValues[6], NULL, -1, 127},</v>
+      </c>
+      <c r="M8" s="76" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">  -1,  // FootSw 2 CC</v>
+      </c>
+      <c r="N8" s="53" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">  m_footsw2,</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="21">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C9" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="D7" s="20">
-        <v>-1</v>
-      </c>
-      <c r="E7" s="20">
-        <v>-1</v>
-      </c>
-      <c r="F7" s="20">
-        <v>-1</v>
-      </c>
-      <c r="G7" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="H7" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="I7" s="43" t="str">
+      <c r="D9" s="20">
+        <v>-1</v>
+      </c>
+      <c r="E9" s="20">
+        <v>-1</v>
+      </c>
+      <c r="F9" s="20">
+        <v>-1</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="I9" s="43" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">"Keyboard", </v>
       </c>
-      <c r="J7" s="44" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="K7" s="44" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="L7" s="40" t="str">
+      <c r="J9" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="K9" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="L9" s="40" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">  {"Keyboard", m_kbd_driver, NULL, NULL, -1, -1},</v>
       </c>
-      <c r="M7" s="76" t="str">
+      <c r="M9" s="76" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">  -1,  // Keyboard</v>
       </c>
-      <c r="N7" s="53" t="str">
-        <f>CONCATENATE("  ",C7,",")</f>
+      <c r="N9" s="53" t="str">
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  m_kbd_driver,</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
+    <row r="10" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="21">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C10" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="D8" s="20">
-        <v>-1</v>
-      </c>
-      <c r="E8" s="20">
-        <v>-1</v>
-      </c>
-      <c r="F8" s="20">
-        <v>-1</v>
-      </c>
-      <c r="G8" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="H8" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="I8" s="43" t="str">
+      <c r="D10" s="20">
+        <v>-1</v>
+      </c>
+      <c r="E10" s="20">
+        <v>-1</v>
+      </c>
+      <c r="F10" s="20">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="H10" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="I10" s="43" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">"Pot Assign", </v>
       </c>
-      <c r="J8" s="44" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="K8" s="44" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="L8" s="40" t="str">
+      <c r="J10" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="K10" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="L10" s="40" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">  {"Pot Assign", m_pot_assign, NULL, NULL, -1, -1},</v>
       </c>
-      <c r="M8" s="76" t="str">
+      <c r="M10" s="76" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">  -1,  // Pot Assign</v>
       </c>
-      <c r="N8" s="53" t="str">
-        <f>CONCATENATE("  ",C8,",")</f>
+      <c r="N10" s="53" t="str">
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  m_pot_assign,</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
+    <row r="11" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="21">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C11" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="D9" s="20">
-        <v>-1</v>
-      </c>
-      <c r="E9" s="20">
-        <v>-1</v>
-      </c>
-      <c r="F9" s="20">
-        <v>-1</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="I9" s="43" t="str">
+      <c r="D11" s="20">
+        <v>-1</v>
+      </c>
+      <c r="E11" s="20">
+        <v>-1</v>
+      </c>
+      <c r="F11" s="20">
+        <v>-1</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="I11" s="43" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">"Button Assign", </v>
       </c>
-      <c r="J9" s="44" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="K9" s="44" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="L9" s="40" t="str">
+      <c r="J11" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="K11" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="L11" s="40" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">  {"Button Assign", m_btn_assign, NULL, NULL, -1, -1},</v>
       </c>
-      <c r="M9" s="76" t="str">
+      <c r="M11" s="76" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">  -1,  // Button Assign</v>
       </c>
-      <c r="N9" s="53" t="str">
-        <f>CONCATENATE("  ",C9,",")</f>
+      <c r="N11" s="53" t="str">
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  m_btn_assign,</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="21">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
+    <row r="12" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C12" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="D10" s="20">
-        <v>-1</v>
-      </c>
-      <c r="E10" s="20">
-        <v>-1</v>
-      </c>
-      <c r="F10" s="20">
-        <v>-1</v>
-      </c>
-      <c r="G10" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="H10" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="I10" s="43" t="str">
+      <c r="D12" s="20">
+        <v>-1</v>
+      </c>
+      <c r="E12" s="20">
+        <v>-1</v>
+      </c>
+      <c r="F12" s="20">
+        <v>-1</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="43" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">"Button Mode", </v>
       </c>
-      <c r="J10" s="44" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="K10" s="44" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="L10" s="40" t="str">
+      <c r="J12" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="K12" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="L12" s="40" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">  {"Button Mode", m_btn_mode, NULL, NULL, -1, -1},</v>
       </c>
-      <c r="M10" s="76" t="str">
+      <c r="M12" s="76" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">  -1,  // Button Mode</v>
       </c>
-      <c r="N10" s="53" t="str">
-        <f>CONCATENATE("  ",C10,",")</f>
+      <c r="N12" s="53" t="str">
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  m_btn_mode,</v>
       </c>
     </row>
-    <row r="11" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="B11" s="1" t="s">
+    <row r="13" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="21">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C13" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="D11" s="20">
-        <v>-1</v>
-      </c>
-      <c r="E11" s="1">
-        <v>-1</v>
-      </c>
-      <c r="F11" s="20">
-        <v>-1</v>
-      </c>
-      <c r="G11" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="H11" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="I11" s="43" t="str">
+      <c r="D13" s="20">
+        <v>-1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F13" s="20">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="I13" s="43" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">"End", </v>
       </c>
-      <c r="J11" s="44" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="K11" s="44" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="L11" s="40" t="str">
+      <c r="J13" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="K13" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="L13" s="40" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">  {"End", m_main_end, NULL, NULL, -1, -1},</v>
       </c>
-      <c r="M11" s="76" t="str">
+      <c r="M13" s="76" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">  -1,  // End</v>
       </c>
-      <c r="N11" s="53" t="str">
-        <f>CONCATENATE("  ",C11,",")</f>
+      <c r="N13" s="53" t="str">
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  m_main_end,</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="21">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="D12" s="20">
-        <v>-1</v>
-      </c>
-      <c r="E12" s="20">
-        <v>127</v>
-      </c>
-      <c r="F12" s="20">
-        <v>-1</v>
-      </c>
-      <c r="G12" s="29" t="str">
-        <f>CONCATENATE("MenuValues[",A12,"]")</f>
-        <v>MenuValues[10]</v>
-      </c>
-      <c r="H12" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="I12" s="43" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">"Pot 1 CC", </v>
-      </c>
-      <c r="J12" s="44" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">&amp;MenuValues[10], </v>
-      </c>
-      <c r="K12" s="44" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="L12" s="40" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Pot 1 CC", m_pot_assign, &amp;MenuValues[10], NULL, -1, 127},</v>
-      </c>
-      <c r="M12" s="76" t="str">
-        <f xml:space="preserve"> CONCATENATE("  ",F12,",  // ",B12)</f>
-        <v xml:space="preserve">  -1,  // Pot 1 CC</v>
-      </c>
-      <c r="N12" s="53" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="21">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="D13" s="20">
-        <v>-1</v>
-      </c>
-      <c r="E13" s="20">
-        <v>127</v>
-      </c>
-      <c r="F13" s="20">
-        <v>-1</v>
-      </c>
-      <c r="G13" s="29" t="str">
-        <f>CONCATENATE("MenuValues[",A13,"]")</f>
-        <v>MenuValues[11]</v>
-      </c>
-      <c r="H13" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="I13" s="43" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">"Pot 2 CC", </v>
-      </c>
-      <c r="J13" s="44" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">&amp;MenuValues[11], </v>
-      </c>
-      <c r="K13" s="44" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="L13" s="40" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Pot 2 CC", m_pot_assign, &amp;MenuValues[11], NULL, -1, 127},</v>
-      </c>
-      <c r="M13" s="76" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Pot 2 CC</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -2085,8 +2102,8 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>11</v>
+      <c r="B14" s="14" t="s">
+        <v>9</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>170</v>
@@ -2109,7 +2126,7 @@
       </c>
       <c r="I14" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Pot 3 CC", </v>
+        <v xml:space="preserve">"Pot 1 CC", </v>
       </c>
       <c r="J14" s="44" t="str">
         <f t="shared" si="3"/>
@@ -2121,11 +2138,14 @@
       </c>
       <c r="L14" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Pot 3 CC", m_pot_assign, &amp;MenuValues[12], NULL, -1, 127},</v>
+        <v xml:space="preserve">  {"Pot 1 CC", m_pot_assign, &amp;MenuValues[12], NULL, -1, 127},</v>
       </c>
       <c r="M14" s="76" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Pot 3 CC</v>
+        <f xml:space="preserve"> CONCATENATE("  ",F14,",  // ",B14)</f>
+        <v xml:space="preserve">  -1,  // Pot 1 CC</v>
+      </c>
+      <c r="N14" s="53" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -2134,7 +2154,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>170</v>
@@ -2157,7 +2177,7 @@
       </c>
       <c r="I15" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Pot 4 CC", </v>
+        <v xml:space="preserve">"Pot 2 CC", </v>
       </c>
       <c r="J15" s="44" t="str">
         <f t="shared" si="3"/>
@@ -2169,11 +2189,11 @@
       </c>
       <c r="L15" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Pot 4 CC", m_pot_assign, &amp;MenuValues[13], NULL, -1, 127},</v>
+        <v xml:space="preserve">  {"Pot 2 CC", m_pot_assign, &amp;MenuValues[13], NULL, -1, 127},</v>
       </c>
       <c r="M15" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Pot 4 CC</v>
+        <v xml:space="preserve">  -1,  // Pot 2 CC</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -2181,34 +2201,35 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="B16" s="13" t="s">
-        <v>173</v>
+      <c r="B16" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="D16" s="61">
-        <v>-1</v>
-      </c>
-      <c r="E16" s="61">
-        <v>-1</v>
-      </c>
-      <c r="F16" s="61">
-        <v>-1</v>
-      </c>
-      <c r="G16" s="29" t="s">
-        <v>96</v>
+      <c r="D16" s="20">
+        <v>-1</v>
+      </c>
+      <c r="E16" s="20">
+        <v>127</v>
+      </c>
+      <c r="F16" s="20">
+        <v>-1</v>
+      </c>
+      <c r="G16" s="29" t="str">
+        <f>CONCATENATE("MenuValues[",A16,"]")</f>
+        <v>MenuValues[14]</v>
       </c>
       <c r="H16" s="29" t="s">
         <v>96</v>
       </c>
       <c r="I16" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Pot CC", </v>
+        <v xml:space="preserve">"Pot 3 CC", </v>
       </c>
       <c r="J16" s="44" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">NULL, </v>
+        <v xml:space="preserve">&amp;MenuValues[14], </v>
       </c>
       <c r="K16" s="44" t="str">
         <f t="shared" si="4"/>
@@ -2216,24 +2237,23 @@
       </c>
       <c r="L16" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Pot CC", m_pot_assign, NULL, NULL, -1, -1},</v>
+        <v xml:space="preserve">  {"Pot 3 CC", m_pot_assign, &amp;MenuValues[14], NULL, -1, 127},</v>
       </c>
       <c r="M16" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Pot CC</v>
-      </c>
-      <c r="N16" s="7"/>
+        <v xml:space="preserve">  -1,  // Pot 3 CC</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="21">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="B17" s="14" t="s">
-        <v>43</v>
+      <c r="B17" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D17" s="20">
         <v>-1</v>
@@ -2245,7 +2265,7 @@
         <v>-1</v>
       </c>
       <c r="G17" s="29" t="str">
-        <f t="shared" ref="G17:G32" si="13">CONCATENATE("MenuValues[",A17,"]")</f>
+        <f>CONCATENATE("MenuValues[",A17,"]")</f>
         <v>MenuValues[15]</v>
       </c>
       <c r="H17" s="29" t="s">
@@ -2253,7 +2273,7 @@
       </c>
       <c r="I17" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 1 CC/Prg", </v>
+        <v xml:space="preserve">"Pot 4 CC", </v>
       </c>
       <c r="J17" s="44" t="str">
         <f t="shared" si="3"/>
@@ -2265,48 +2285,46 @@
       </c>
       <c r="L17" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Btn 1 CC/Prg", m_btn_assign, &amp;MenuValues[15], NULL, -1, 127},</v>
+        <v xml:space="preserve">  {"Pot 4 CC", m_pot_assign, &amp;MenuValues[15], NULL, -1, 127},</v>
       </c>
       <c r="M17" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Btn 1 CC/Prg</v>
-      </c>
-      <c r="N17" s="7"/>
-    </row>
-    <row r="18" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">  -1,  // Pot 4 CC</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="21">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>44</v>
+      <c r="B18" s="13" t="s">
+        <v>173</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="D18" s="20">
-        <v>-1</v>
-      </c>
-      <c r="E18" s="20">
-        <v>127</v>
-      </c>
-      <c r="F18" s="20">
-        <v>-1</v>
-      </c>
-      <c r="G18" s="29" t="str">
-        <f t="shared" si="13"/>
-        <v>MenuValues[16]</v>
+        <v>170</v>
+      </c>
+      <c r="D18" s="61">
+        <v>-1</v>
+      </c>
+      <c r="E18" s="61">
+        <v>-1</v>
+      </c>
+      <c r="F18" s="61">
+        <v>-1</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>96</v>
       </c>
       <c r="H18" s="29" t="s">
         <v>96</v>
       </c>
       <c r="I18" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 2 CC/Prg", </v>
+        <v xml:space="preserve">"Pot CC", </v>
       </c>
       <c r="J18" s="44" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">&amp;MenuValues[16], </v>
+        <v xml:space="preserve">NULL, </v>
       </c>
       <c r="K18" s="44" t="str">
         <f t="shared" si="4"/>
@@ -2314,11 +2332,11 @@
       </c>
       <c r="L18" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Btn 2 CC/Prg", m_btn_assign, &amp;MenuValues[16], NULL, -1, 127},</v>
+        <v xml:space="preserve">  {"Pot CC", m_pot_assign, NULL, NULL, -1, -1},</v>
       </c>
       <c r="M18" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Btn 2 CC/Prg</v>
+        <v xml:space="preserve">  -1,  // Pot CC</v>
       </c>
       <c r="N18" s="7"/>
     </row>
@@ -2327,8 +2345,8 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>45</v>
+      <c r="B19" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>171</v>
@@ -2343,7 +2361,7 @@
         <v>-1</v>
       </c>
       <c r="G19" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="G19:G34" si="21">CONCATENATE("MenuValues[",A19,"]")</f>
         <v>MenuValues[17]</v>
       </c>
       <c r="H19" s="29" t="s">
@@ -2351,7 +2369,7 @@
       </c>
       <c r="I19" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 3 CC/Prg", </v>
+        <v xml:space="preserve">"Btn 1 CC/Prg", </v>
       </c>
       <c r="J19" s="44" t="str">
         <f t="shared" si="3"/>
@@ -2363,21 +2381,21 @@
       </c>
       <c r="L19" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Btn 3 CC/Prg", m_btn_assign, &amp;MenuValues[17], NULL, -1, 127},</v>
+        <v xml:space="preserve">  {"Btn 1 CC/Prg", m_btn_assign, &amp;MenuValues[17], NULL, -1, 127},</v>
       </c>
       <c r="M19" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Btn 3 CC/Prg</v>
+        <v xml:space="preserve">  -1,  // Btn 1 CC/Prg</v>
       </c>
       <c r="N19" s="7"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="21">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>171</v>
@@ -2392,7 +2410,7 @@
         <v>-1</v>
       </c>
       <c r="G20" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>MenuValues[18]</v>
       </c>
       <c r="H20" s="29" t="s">
@@ -2400,7 +2418,7 @@
       </c>
       <c r="I20" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 4 CC/Prg", </v>
+        <v xml:space="preserve">"Btn 2 CC/Prg", </v>
       </c>
       <c r="J20" s="44" t="str">
         <f t="shared" si="3"/>
@@ -2412,11 +2430,11 @@
       </c>
       <c r="L20" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Btn 4 CC/Prg", m_btn_assign, &amp;MenuValues[18], NULL, -1, 127},</v>
+        <v xml:space="preserve">  {"Btn 2 CC/Prg", m_btn_assign, &amp;MenuValues[18], NULL, -1, 127},</v>
       </c>
       <c r="M20" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Btn 4 CC/Prg</v>
+        <v xml:space="preserve">  -1,  // Btn 2 CC/Prg</v>
       </c>
       <c r="N20" s="7"/>
     </row>
@@ -2426,7 +2444,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>171</v>
@@ -2441,7 +2459,7 @@
         <v>-1</v>
       </c>
       <c r="G21" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>MenuValues[19]</v>
       </c>
       <c r="H21" s="29" t="s">
@@ -2449,7 +2467,7 @@
       </c>
       <c r="I21" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 5 CC/Prg", </v>
+        <v xml:space="preserve">"Btn 3 CC/Prg", </v>
       </c>
       <c r="J21" s="44" t="str">
         <f t="shared" si="3"/>
@@ -2461,11 +2479,11 @@
       </c>
       <c r="L21" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Btn 5 CC/Prg", m_btn_assign, &amp;MenuValues[19], NULL, -1, 127},</v>
+        <v xml:space="preserve">  {"Btn 3 CC/Prg", m_btn_assign, &amp;MenuValues[19], NULL, -1, 127},</v>
       </c>
       <c r="M21" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Btn 5 CC/Prg</v>
+        <v xml:space="preserve">  -1,  // Btn 3 CC/Prg</v>
       </c>
       <c r="N21" s="7"/>
     </row>
@@ -2475,7 +2493,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>171</v>
@@ -2490,7 +2508,7 @@
         <v>-1</v>
       </c>
       <c r="G22" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>MenuValues[20]</v>
       </c>
       <c r="H22" s="29" t="s">
@@ -2498,7 +2516,7 @@
       </c>
       <c r="I22" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 6 CC/Prg", </v>
+        <v xml:space="preserve">"Btn 4 CC/Prg", </v>
       </c>
       <c r="J22" s="44" t="str">
         <f t="shared" si="3"/>
@@ -2510,11 +2528,11 @@
       </c>
       <c r="L22" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Btn 6 CC/Prg", m_btn_assign, &amp;MenuValues[20], NULL, -1, 127},</v>
+        <v xml:space="preserve">  {"Btn 4 CC/Prg", m_btn_assign, &amp;MenuValues[20], NULL, -1, 127},</v>
       </c>
       <c r="M22" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Btn 6 CC/Prg</v>
+        <v xml:space="preserve">  -1,  // Btn 4 CC/Prg</v>
       </c>
       <c r="N22" s="7"/>
     </row>
@@ -2524,7 +2542,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>171</v>
@@ -2539,7 +2557,7 @@
         <v>-1</v>
       </c>
       <c r="G23" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>MenuValues[21]</v>
       </c>
       <c r="H23" s="29" t="s">
@@ -2547,7 +2565,7 @@
       </c>
       <c r="I23" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 7 CC/Prg", </v>
+        <v xml:space="preserve">"Btn 5 CC/Prg", </v>
       </c>
       <c r="J23" s="44" t="str">
         <f t="shared" si="3"/>
@@ -2559,11 +2577,11 @@
       </c>
       <c r="L23" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Btn 7 CC/Prg", m_btn_assign, &amp;MenuValues[21], NULL, -1, 127},</v>
+        <v xml:space="preserve">  {"Btn 5 CC/Prg", m_btn_assign, &amp;MenuValues[21], NULL, -1, 127},</v>
       </c>
       <c r="M23" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Btn 7 CC/Prg</v>
+        <v xml:space="preserve">  -1,  // Btn 5 CC/Prg</v>
       </c>
       <c r="N23" s="7"/>
     </row>
@@ -2573,7 +2591,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C24" s="20" t="s">
         <v>171</v>
@@ -2588,7 +2606,7 @@
         <v>-1</v>
       </c>
       <c r="G24" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>MenuValues[22]</v>
       </c>
       <c r="H24" s="29" t="s">
@@ -2596,7 +2614,7 @@
       </c>
       <c r="I24" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 8 CC/Prg", </v>
+        <v xml:space="preserve">"Btn 6 CC/Prg", </v>
       </c>
       <c r="J24" s="44" t="str">
         <f t="shared" si="3"/>
@@ -2608,11 +2626,11 @@
       </c>
       <c r="L24" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Btn 8 CC/Prg", m_btn_assign, &amp;MenuValues[22], NULL, -1, 127},</v>
+        <v xml:space="preserve">  {"Btn 6 CC/Prg", m_btn_assign, &amp;MenuValues[22], NULL, -1, 127},</v>
       </c>
       <c r="M24" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Btn 8 CC/Prg</v>
+        <v xml:space="preserve">  -1,  // Btn 6 CC/Prg</v>
       </c>
       <c r="N24" s="7"/>
     </row>
@@ -2622,7 +2640,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C25" s="20" t="s">
         <v>171</v>
@@ -2637,7 +2655,7 @@
         <v>-1</v>
       </c>
       <c r="G25" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>MenuValues[23]</v>
       </c>
       <c r="H25" s="29" t="s">
@@ -2645,7 +2663,7 @@
       </c>
       <c r="I25" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 9 CC/Prg", </v>
+        <v xml:space="preserve">"Btn 7 CC/Prg", </v>
       </c>
       <c r="J25" s="44" t="str">
         <f t="shared" si="3"/>
@@ -2657,13 +2675,13 @@
       </c>
       <c r="L25" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Btn 9 CC/Prg", m_btn_assign, &amp;MenuValues[23], NULL, -1, 127},</v>
+        <v xml:space="preserve">  {"Btn 7 CC/Prg", m_btn_assign, &amp;MenuValues[23], NULL, -1, 127},</v>
       </c>
       <c r="M25" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Btn 9 CC/Prg</v>
-      </c>
-      <c r="N25" s="11"/>
+        <v xml:space="preserve">  -1,  // Btn 7 CC/Prg</v>
+      </c>
+      <c r="N25" s="7"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="21">
@@ -2671,7 +2689,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>171</v>
@@ -2686,7 +2704,7 @@
         <v>-1</v>
       </c>
       <c r="G26" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>MenuValues[24]</v>
       </c>
       <c r="H26" s="29" t="s">
@@ -2694,7 +2712,7 @@
       </c>
       <c r="I26" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 10 CC/Prg", </v>
+        <v xml:space="preserve">"Btn 8 CC/Prg", </v>
       </c>
       <c r="J26" s="44" t="str">
         <f t="shared" si="3"/>
@@ -2706,13 +2724,13 @@
       </c>
       <c r="L26" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Btn 10 CC/Prg", m_btn_assign, &amp;MenuValues[24], NULL, -1, 127},</v>
+        <v xml:space="preserve">  {"Btn 8 CC/Prg", m_btn_assign, &amp;MenuValues[24], NULL, -1, 127},</v>
       </c>
       <c r="M26" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Btn 10 CC/Prg</v>
-      </c>
-      <c r="N26" s="11"/>
+        <v xml:space="preserve">  -1,  // Btn 8 CC/Prg</v>
+      </c>
+      <c r="N26" s="7"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="21">
@@ -2720,7 +2738,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C27" s="20" t="s">
         <v>171</v>
@@ -2735,7 +2753,7 @@
         <v>-1</v>
       </c>
       <c r="G27" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>MenuValues[25]</v>
       </c>
       <c r="H27" s="29" t="s">
@@ -2743,7 +2761,7 @@
       </c>
       <c r="I27" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 11 CC/Prg", </v>
+        <v xml:space="preserve">"Btn 9 CC/Prg", </v>
       </c>
       <c r="J27" s="44" t="str">
         <f t="shared" si="3"/>
@@ -2755,11 +2773,11 @@
       </c>
       <c r="L27" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Btn 11 CC/Prg", m_btn_assign, &amp;MenuValues[25], NULL, -1, 127},</v>
+        <v xml:space="preserve">  {"Btn 9 CC/Prg", m_btn_assign, &amp;MenuValues[25], NULL, -1, 127},</v>
       </c>
       <c r="M27" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Btn 11 CC/Prg</v>
+        <v xml:space="preserve">  -1,  // Btn 9 CC/Prg</v>
       </c>
       <c r="N27" s="11"/>
     </row>
@@ -2769,7 +2787,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C28" s="20" t="s">
         <v>171</v>
@@ -2784,7 +2802,7 @@
         <v>-1</v>
       </c>
       <c r="G28" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>MenuValues[26]</v>
       </c>
       <c r="H28" s="29" t="s">
@@ -2792,7 +2810,7 @@
       </c>
       <c r="I28" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 12 CC/Prg", </v>
+        <v xml:space="preserve">"Btn 10 CC/Prg", </v>
       </c>
       <c r="J28" s="44" t="str">
         <f t="shared" si="3"/>
@@ -2804,11 +2822,11 @@
       </c>
       <c r="L28" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Btn 12 CC/Prg", m_btn_assign, &amp;MenuValues[26], NULL, -1, 127},</v>
+        <v xml:space="preserve">  {"Btn 10 CC/Prg", m_btn_assign, &amp;MenuValues[26], NULL, -1, 127},</v>
       </c>
       <c r="M28" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Btn 12 CC/Prg</v>
+        <v xml:space="preserve">  -1,  // Btn 10 CC/Prg</v>
       </c>
       <c r="N28" s="11"/>
     </row>
@@ -2818,7 +2836,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C29" s="20" t="s">
         <v>171</v>
@@ -2833,7 +2851,7 @@
         <v>-1</v>
       </c>
       <c r="G29" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>MenuValues[27]</v>
       </c>
       <c r="H29" s="29" t="s">
@@ -2841,7 +2859,7 @@
       </c>
       <c r="I29" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 13 CC/Prg", </v>
+        <v xml:space="preserve">"Btn 11 CC/Prg", </v>
       </c>
       <c r="J29" s="44" t="str">
         <f t="shared" si="3"/>
@@ -2853,11 +2871,11 @@
       </c>
       <c r="L29" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Btn 13 CC/Prg", m_btn_assign, &amp;MenuValues[27], NULL, -1, 127},</v>
+        <v xml:space="preserve">  {"Btn 11 CC/Prg", m_btn_assign, &amp;MenuValues[27], NULL, -1, 127},</v>
       </c>
       <c r="M29" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Btn 13 CC/Prg</v>
+        <v xml:space="preserve">  -1,  // Btn 11 CC/Prg</v>
       </c>
       <c r="N29" s="11"/>
     </row>
@@ -2867,7 +2885,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C30" s="20" t="s">
         <v>171</v>
@@ -2882,7 +2900,7 @@
         <v>-1</v>
       </c>
       <c r="G30" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>MenuValues[28]</v>
       </c>
       <c r="H30" s="29" t="s">
@@ -2890,7 +2908,7 @@
       </c>
       <c r="I30" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 14 CC/Prg", </v>
+        <v xml:space="preserve">"Btn 12 CC/Prg", </v>
       </c>
       <c r="J30" s="44" t="str">
         <f t="shared" si="3"/>
@@ -2902,11 +2920,11 @@
       </c>
       <c r="L30" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Btn 14 CC/Prg", m_btn_assign, &amp;MenuValues[28], NULL, -1, 127},</v>
+        <v xml:space="preserve">  {"Btn 12 CC/Prg", m_btn_assign, &amp;MenuValues[28], NULL, -1, 127},</v>
       </c>
       <c r="M30" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Btn 14 CC/Prg</v>
+        <v xml:space="preserve">  -1,  // Btn 12 CC/Prg</v>
       </c>
       <c r="N30" s="11"/>
     </row>
@@ -2916,7 +2934,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C31" s="20" t="s">
         <v>171</v>
@@ -2931,7 +2949,7 @@
         <v>-1</v>
       </c>
       <c r="G31" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>MenuValues[29]</v>
       </c>
       <c r="H31" s="29" t="s">
@@ -2939,7 +2957,7 @@
       </c>
       <c r="I31" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 15 CC/Prg", </v>
+        <v xml:space="preserve">"Btn 13 CC/Prg", </v>
       </c>
       <c r="J31" s="44" t="str">
         <f t="shared" si="3"/>
@@ -2951,11 +2969,11 @@
       </c>
       <c r="L31" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Btn 15 CC/Prg", m_btn_assign, &amp;MenuValues[29], NULL, -1, 127},</v>
+        <v xml:space="preserve">  {"Btn 13 CC/Prg", m_btn_assign, &amp;MenuValues[29], NULL, -1, 127},</v>
       </c>
       <c r="M31" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Btn 15 CC/Prg</v>
+        <v xml:space="preserve">  -1,  // Btn 13 CC/Prg</v>
       </c>
       <c r="N31" s="11"/>
     </row>
@@ -2965,7 +2983,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C32" s="20" t="s">
         <v>171</v>
@@ -2980,7 +2998,7 @@
         <v>-1</v>
       </c>
       <c r="G32" s="29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>MenuValues[30]</v>
       </c>
       <c r="H32" s="29" t="s">
@@ -2988,7 +3006,7 @@
       </c>
       <c r="I32" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 16 CC/Prg", </v>
+        <v xml:space="preserve">"Btn 14 CC/Prg", </v>
       </c>
       <c r="J32" s="44" t="str">
         <f t="shared" si="3"/>
@@ -3000,11 +3018,11 @@
       </c>
       <c r="L32" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Btn 16 CC/Prg", m_btn_assign, &amp;MenuValues[30], NULL, -1, 127},</v>
+        <v xml:space="preserve">  {"Btn 14 CC/Prg", m_btn_assign, &amp;MenuValues[30], NULL, -1, 127},</v>
       </c>
       <c r="M32" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Btn 16 CC/Prg</v>
+        <v xml:space="preserve">  -1,  // Btn 14 CC/Prg</v>
       </c>
       <c r="N32" s="11"/>
     </row>
@@ -3013,34 +3031,35 @@
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="B33" s="13" t="s">
-        <v>174</v>
+      <c r="B33" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="C33" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="D33" s="61">
-        <v>-1</v>
-      </c>
-      <c r="E33" s="61">
-        <v>-1</v>
-      </c>
-      <c r="F33" s="61">
-        <v>-1</v>
-      </c>
-      <c r="G33" s="29" t="s">
-        <v>96</v>
+      <c r="D33" s="20">
+        <v>-1</v>
+      </c>
+      <c r="E33" s="20">
+        <v>127</v>
+      </c>
+      <c r="F33" s="20">
+        <v>-1</v>
+      </c>
+      <c r="G33" s="29" t="str">
+        <f t="shared" si="21"/>
+        <v>MenuValues[31]</v>
       </c>
       <c r="H33" s="29" t="s">
         <v>96</v>
       </c>
       <c r="I33" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn CC", </v>
+        <v xml:space="preserve">"Btn 15 CC/Prg", </v>
       </c>
       <c r="J33" s="44" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">NULL, </v>
+        <v xml:space="preserve">&amp;MenuValues[31], </v>
       </c>
       <c r="K33" s="44" t="str">
         <f t="shared" si="4"/>
@@ -3048,11 +3067,11 @@
       </c>
       <c r="L33" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Btn CC", m_btn_assign, NULL, NULL, -1, -1},</v>
+        <v xml:space="preserve">  {"Btn 15 CC/Prg", m_btn_assign, &amp;MenuValues[31], NULL, -1, 127},</v>
       </c>
       <c r="M33" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Btn CC</v>
+        <v xml:space="preserve">  -1,  // Btn 15 CC/Prg</v>
       </c>
       <c r="N33" s="11"/>
     </row>
@@ -3061,31 +3080,31 @@
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
-      <c r="B34" s="14" t="s">
-        <v>26</v>
+      <c r="B34" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D34" s="20">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E34" s="20">
-        <v>3</v>
+        <v>127</v>
       </c>
       <c r="F34" s="20">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G34" s="29" t="str">
-        <f t="shared" ref="G34:G49" si="14">CONCATENATE("MenuValues[",A34,"]")</f>
+        <f t="shared" si="21"/>
         <v>MenuValues[32]</v>
       </c>
       <c r="H34" s="29" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="I34" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 1 Mode", </v>
+        <v xml:space="preserve">"Btn 16 CC/Prg", </v>
       </c>
       <c r="J34" s="44" t="str">
         <f t="shared" si="3"/>
@@ -3093,15 +3112,15 @@
       </c>
       <c r="K34" s="44" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">&amp;setBtnMode, </v>
+        <v xml:space="preserve">NULL, </v>
       </c>
       <c r="L34" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Btn 1 Mode", m_btn_mode, &amp;MenuValues[32], &amp;setBtnMode, 0, 3},</v>
+        <v xml:space="preserve">  {"Btn 16 CC/Prg", m_btn_assign, &amp;MenuValues[32], NULL, -1, 127},</v>
       </c>
       <c r="M34" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  0,  // Btn 1 Mode</v>
+        <v xml:space="preserve">  -1,  // Btn 16 CC/Prg</v>
       </c>
       <c r="N34" s="11"/>
     </row>
@@ -3110,47 +3129,46 @@
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>27</v>
+      <c r="B35" s="13" t="s">
+        <v>174</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="D35" s="20">
-        <v>0</v>
-      </c>
-      <c r="E35" s="20">
-        <v>3</v>
-      </c>
-      <c r="F35" s="20">
-        <v>0</v>
-      </c>
-      <c r="G35" s="29" t="str">
-        <f t="shared" si="14"/>
-        <v>MenuValues[33]</v>
+        <v>171</v>
+      </c>
+      <c r="D35" s="61">
+        <v>-1</v>
+      </c>
+      <c r="E35" s="61">
+        <v>-1</v>
+      </c>
+      <c r="F35" s="61">
+        <v>-1</v>
+      </c>
+      <c r="G35" s="29" t="s">
+        <v>96</v>
       </c>
       <c r="H35" s="29" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="I35" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 2 Mode", </v>
+        <v xml:space="preserve">"Btn CC", </v>
       </c>
       <c r="J35" s="44" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">&amp;MenuValues[33], </v>
+        <v xml:space="preserve">NULL, </v>
       </c>
       <c r="K35" s="44" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">&amp;setBtnMode, </v>
+        <v xml:space="preserve">NULL, </v>
       </c>
       <c r="L35" s="40" t="str">
-        <f t="shared" ref="L35:L66" si="15">CONCATENATE("  {",I35,C35,", ",J35,K35,D35,", ",E35,"},")</f>
-        <v xml:space="preserve">  {"Btn 2 Mode", m_btn_mode, &amp;MenuValues[33], &amp;setBtnMode, 0, 3},</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">  {"Btn CC", m_btn_assign, NULL, NULL, -1, -1},</v>
       </c>
       <c r="M35" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  0,  // Btn 2 Mode</v>
+        <v xml:space="preserve">  -1,  // Btn CC</v>
       </c>
       <c r="N35" s="11"/>
     </row>
@@ -3159,8 +3177,8 @@
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>28</v>
+      <c r="B36" s="14" t="s">
+        <v>26</v>
       </c>
       <c r="C36" s="20" t="s">
         <v>172</v>
@@ -3175,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="G36:G51" si="22">CONCATENATE("MenuValues[",A36,"]")</f>
         <v>MenuValues[34]</v>
       </c>
       <c r="H36" s="29" t="s">
@@ -3183,7 +3201,7 @@
       </c>
       <c r="I36" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 3 Mode", </v>
+        <v xml:space="preserve">"Btn 1 Mode", </v>
       </c>
       <c r="J36" s="44" t="str">
         <f t="shared" si="3"/>
@@ -3194,12 +3212,12 @@
         <v xml:space="preserve">&amp;setBtnMode, </v>
       </c>
       <c r="L36" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">  {"Btn 3 Mode", m_btn_mode, &amp;MenuValues[34], &amp;setBtnMode, 0, 3},</v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">  {"Btn 1 Mode", m_btn_mode, &amp;MenuValues[34], &amp;setBtnMode, 0, 3},</v>
       </c>
       <c r="M36" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  0,  // Btn 3 Mode</v>
+        <v xml:space="preserve">  0,  // Btn 1 Mode</v>
       </c>
       <c r="N36" s="11"/>
     </row>
@@ -3209,7 +3227,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C37" s="20" t="s">
         <v>172</v>
@@ -3224,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>MenuValues[35]</v>
       </c>
       <c r="H37" s="29" t="s">
@@ -3232,7 +3250,7 @@
       </c>
       <c r="I37" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 4 Mode", </v>
+        <v xml:space="preserve">"Btn 2 Mode", </v>
       </c>
       <c r="J37" s="44" t="str">
         <f t="shared" si="3"/>
@@ -3243,12 +3261,12 @@
         <v xml:space="preserve">&amp;setBtnMode, </v>
       </c>
       <c r="L37" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">  {"Btn 4 Mode", m_btn_mode, &amp;MenuValues[35], &amp;setBtnMode, 0, 3},</v>
+        <f t="shared" ref="L37:L56" si="23">CONCATENATE("  {",I37,C37,", ",J37,K37,D37,", ",E37,"},")</f>
+        <v xml:space="preserve">  {"Btn 2 Mode", m_btn_mode, &amp;MenuValues[35], &amp;setBtnMode, 0, 3},</v>
       </c>
       <c r="M37" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  0,  // Btn 4 Mode</v>
+        <v xml:space="preserve">  0,  // Btn 2 Mode</v>
       </c>
       <c r="N37" s="11"/>
     </row>
@@ -3258,7 +3276,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C38" s="20" t="s">
         <v>172</v>
@@ -3273,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>MenuValues[36]</v>
       </c>
       <c r="H38" s="29" t="s">
@@ -3281,7 +3299,7 @@
       </c>
       <c r="I38" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 5 Mode", </v>
+        <v xml:space="preserve">"Btn 3 Mode", </v>
       </c>
       <c r="J38" s="44" t="str">
         <f t="shared" si="3"/>
@@ -3292,12 +3310,12 @@
         <v xml:space="preserve">&amp;setBtnMode, </v>
       </c>
       <c r="L38" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">  {"Btn 5 Mode", m_btn_mode, &amp;MenuValues[36], &amp;setBtnMode, 0, 3},</v>
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">  {"Btn 3 Mode", m_btn_mode, &amp;MenuValues[36], &amp;setBtnMode, 0, 3},</v>
       </c>
       <c r="M38" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  0,  // Btn 5 Mode</v>
+        <v xml:space="preserve">  0,  // Btn 3 Mode</v>
       </c>
       <c r="N38" s="11"/>
     </row>
@@ -3307,7 +3325,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C39" s="20" t="s">
         <v>172</v>
@@ -3322,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>MenuValues[37]</v>
       </c>
       <c r="H39" s="29" t="s">
@@ -3330,7 +3348,7 @@
       </c>
       <c r="I39" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 6 Mode", </v>
+        <v xml:space="preserve">"Btn 4 Mode", </v>
       </c>
       <c r="J39" s="44" t="str">
         <f t="shared" si="3"/>
@@ -3341,12 +3359,12 @@
         <v xml:space="preserve">&amp;setBtnMode, </v>
       </c>
       <c r="L39" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">  {"Btn 6 Mode", m_btn_mode, &amp;MenuValues[37], &amp;setBtnMode, 0, 3},</v>
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">  {"Btn 4 Mode", m_btn_mode, &amp;MenuValues[37], &amp;setBtnMode, 0, 3},</v>
       </c>
       <c r="M39" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  0,  // Btn 6 Mode</v>
+        <v xml:space="preserve">  0,  // Btn 4 Mode</v>
       </c>
       <c r="N39" s="11"/>
     </row>
@@ -3356,7 +3374,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C40" s="20" t="s">
         <v>172</v>
@@ -3371,7 +3389,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>MenuValues[38]</v>
       </c>
       <c r="H40" s="29" t="s">
@@ -3379,7 +3397,7 @@
       </c>
       <c r="I40" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 7 Mode", </v>
+        <v xml:space="preserve">"Btn 5 Mode", </v>
       </c>
       <c r="J40" s="44" t="str">
         <f t="shared" si="3"/>
@@ -3390,12 +3408,12 @@
         <v xml:space="preserve">&amp;setBtnMode, </v>
       </c>
       <c r="L40" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">  {"Btn 7 Mode", m_btn_mode, &amp;MenuValues[38], &amp;setBtnMode, 0, 3},</v>
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">  {"Btn 5 Mode", m_btn_mode, &amp;MenuValues[38], &amp;setBtnMode, 0, 3},</v>
       </c>
       <c r="M40" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  0,  // Btn 7 Mode</v>
+        <v xml:space="preserve">  0,  // Btn 5 Mode</v>
       </c>
       <c r="N40" s="11"/>
     </row>
@@ -3405,7 +3423,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C41" s="20" t="s">
         <v>172</v>
@@ -3420,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>MenuValues[39]</v>
       </c>
       <c r="H41" s="29" t="s">
@@ -3428,7 +3446,7 @@
       </c>
       <c r="I41" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 8 Mode", </v>
+        <v xml:space="preserve">"Btn 6 Mode", </v>
       </c>
       <c r="J41" s="44" t="str">
         <f t="shared" si="3"/>
@@ -3439,12 +3457,12 @@
         <v xml:space="preserve">&amp;setBtnMode, </v>
       </c>
       <c r="L41" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">  {"Btn 8 Mode", m_btn_mode, &amp;MenuValues[39], &amp;setBtnMode, 0, 3},</v>
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">  {"Btn 6 Mode", m_btn_mode, &amp;MenuValues[39], &amp;setBtnMode, 0, 3},</v>
       </c>
       <c r="M41" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  0,  // Btn 8 Mode</v>
+        <v xml:space="preserve">  0,  // Btn 6 Mode</v>
       </c>
       <c r="N41" s="11"/>
     </row>
@@ -3454,7 +3472,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C42" s="20" t="s">
         <v>172</v>
@@ -3469,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>MenuValues[40]</v>
       </c>
       <c r="H42" s="29" t="s">
@@ -3477,7 +3495,7 @@
       </c>
       <c r="I42" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 9 Mode", </v>
+        <v xml:space="preserve">"Btn 7 Mode", </v>
       </c>
       <c r="J42" s="44" t="str">
         <f t="shared" si="3"/>
@@ -3488,12 +3506,12 @@
         <v xml:space="preserve">&amp;setBtnMode, </v>
       </c>
       <c r="L42" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">  {"Btn 9 Mode", m_btn_mode, &amp;MenuValues[40], &amp;setBtnMode, 0, 3},</v>
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">  {"Btn 7 Mode", m_btn_mode, &amp;MenuValues[40], &amp;setBtnMode, 0, 3},</v>
       </c>
       <c r="M42" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  0,  // Btn 9 Mode</v>
+        <v xml:space="preserve">  0,  // Btn 7 Mode</v>
       </c>
       <c r="N42" s="11"/>
     </row>
@@ -3503,7 +3521,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C43" s="20" t="s">
         <v>172</v>
@@ -3518,7 +3536,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>MenuValues[41]</v>
       </c>
       <c r="H43" s="29" t="s">
@@ -3526,7 +3544,7 @@
       </c>
       <c r="I43" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 10 Mode", </v>
+        <v xml:space="preserve">"Btn 8 Mode", </v>
       </c>
       <c r="J43" s="44" t="str">
         <f t="shared" si="3"/>
@@ -3537,12 +3555,12 @@
         <v xml:space="preserve">&amp;setBtnMode, </v>
       </c>
       <c r="L43" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">  {"Btn 10 Mode", m_btn_mode, &amp;MenuValues[41], &amp;setBtnMode, 0, 3},</v>
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">  {"Btn 8 Mode", m_btn_mode, &amp;MenuValues[41], &amp;setBtnMode, 0, 3},</v>
       </c>
       <c r="M43" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  0,  // Btn 10 Mode</v>
+        <v xml:space="preserve">  0,  // Btn 8 Mode</v>
       </c>
       <c r="N43" s="11"/>
     </row>
@@ -3552,7 +3570,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C44" s="20" t="s">
         <v>172</v>
@@ -3567,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>MenuValues[42]</v>
       </c>
       <c r="H44" s="29" t="s">
@@ -3575,7 +3593,7 @@
       </c>
       <c r="I44" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 11 Mode", </v>
+        <v xml:space="preserve">"Btn 9 Mode", </v>
       </c>
       <c r="J44" s="44" t="str">
         <f t="shared" si="3"/>
@@ -3586,12 +3604,12 @@
         <v xml:space="preserve">&amp;setBtnMode, </v>
       </c>
       <c r="L44" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">  {"Btn 11 Mode", m_btn_mode, &amp;MenuValues[42], &amp;setBtnMode, 0, 3},</v>
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">  {"Btn 9 Mode", m_btn_mode, &amp;MenuValues[42], &amp;setBtnMode, 0, 3},</v>
       </c>
       <c r="M44" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  0,  // Btn 11 Mode</v>
+        <v xml:space="preserve">  0,  // Btn 9 Mode</v>
       </c>
       <c r="N44" s="11"/>
     </row>
@@ -3601,7 +3619,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C45" s="20" t="s">
         <v>172</v>
@@ -3616,7 +3634,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>MenuValues[43]</v>
       </c>
       <c r="H45" s="29" t="s">
@@ -3624,7 +3642,7 @@
       </c>
       <c r="I45" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 12 Mode", </v>
+        <v xml:space="preserve">"Btn 10 Mode", </v>
       </c>
       <c r="J45" s="44" t="str">
         <f t="shared" si="3"/>
@@ -3635,12 +3653,12 @@
         <v xml:space="preserve">&amp;setBtnMode, </v>
       </c>
       <c r="L45" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">  {"Btn 12 Mode", m_btn_mode, &amp;MenuValues[43], &amp;setBtnMode, 0, 3},</v>
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">  {"Btn 10 Mode", m_btn_mode, &amp;MenuValues[43], &amp;setBtnMode, 0, 3},</v>
       </c>
       <c r="M45" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  0,  // Btn 12 Mode</v>
+        <v xml:space="preserve">  0,  // Btn 10 Mode</v>
       </c>
       <c r="N45" s="11"/>
     </row>
@@ -3650,7 +3668,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C46" s="20" t="s">
         <v>172</v>
@@ -3665,7 +3683,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>MenuValues[44]</v>
       </c>
       <c r="H46" s="29" t="s">
@@ -3673,7 +3691,7 @@
       </c>
       <c r="I46" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 13 Mode", </v>
+        <v xml:space="preserve">"Btn 11 Mode", </v>
       </c>
       <c r="J46" s="44" t="str">
         <f t="shared" si="3"/>
@@ -3684,12 +3702,12 @@
         <v xml:space="preserve">&amp;setBtnMode, </v>
       </c>
       <c r="L46" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">  {"Btn 13 Mode", m_btn_mode, &amp;MenuValues[44], &amp;setBtnMode, 0, 3},</v>
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">  {"Btn 11 Mode", m_btn_mode, &amp;MenuValues[44], &amp;setBtnMode, 0, 3},</v>
       </c>
       <c r="M46" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  0,  // Btn 13 Mode</v>
+        <v xml:space="preserve">  0,  // Btn 11 Mode</v>
       </c>
       <c r="N46" s="11"/>
     </row>
@@ -3699,7 +3717,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C47" s="20" t="s">
         <v>172</v>
@@ -3714,7 +3732,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>MenuValues[45]</v>
       </c>
       <c r="H47" s="29" t="s">
@@ -3722,7 +3740,7 @@
       </c>
       <c r="I47" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 14 Mode", </v>
+        <v xml:space="preserve">"Btn 12 Mode", </v>
       </c>
       <c r="J47" s="44" t="str">
         <f t="shared" si="3"/>
@@ -3733,12 +3751,12 @@
         <v xml:space="preserve">&amp;setBtnMode, </v>
       </c>
       <c r="L47" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">  {"Btn 14 Mode", m_btn_mode, &amp;MenuValues[45], &amp;setBtnMode, 0, 3},</v>
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">  {"Btn 12 Mode", m_btn_mode, &amp;MenuValues[45], &amp;setBtnMode, 0, 3},</v>
       </c>
       <c r="M47" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  0,  // Btn 14 Mode</v>
+        <v xml:space="preserve">  0,  // Btn 12 Mode</v>
       </c>
       <c r="N47" s="11"/>
     </row>
@@ -3748,7 +3766,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C48" s="20" t="s">
         <v>172</v>
@@ -3763,7 +3781,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>MenuValues[46]</v>
       </c>
       <c r="H48" s="29" t="s">
@@ -3771,7 +3789,7 @@
       </c>
       <c r="I48" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 15 Mode", </v>
+        <v xml:space="preserve">"Btn 13 Mode", </v>
       </c>
       <c r="J48" s="44" t="str">
         <f t="shared" si="3"/>
@@ -3782,12 +3800,12 @@
         <v xml:space="preserve">&amp;setBtnMode, </v>
       </c>
       <c r="L48" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">  {"Btn 15 Mode", m_btn_mode, &amp;MenuValues[46], &amp;setBtnMode, 0, 3},</v>
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">  {"Btn 13 Mode", m_btn_mode, &amp;MenuValues[46], &amp;setBtnMode, 0, 3},</v>
       </c>
       <c r="M48" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  0,  // Btn 15 Mode</v>
+        <v xml:space="preserve">  0,  // Btn 13 Mode</v>
       </c>
       <c r="N48" s="11"/>
     </row>
@@ -3797,7 +3815,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C49" s="20" t="s">
         <v>172</v>
@@ -3812,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>MenuValues[47]</v>
       </c>
       <c r="H49" s="29" t="s">
@@ -3820,7 +3838,7 @@
       </c>
       <c r="I49" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn 16 Mode", </v>
+        <v xml:space="preserve">"Btn 14 Mode", </v>
       </c>
       <c r="J49" s="44" t="str">
         <f t="shared" si="3"/>
@@ -3831,12 +3849,12 @@
         <v xml:space="preserve">&amp;setBtnMode, </v>
       </c>
       <c r="L49" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">  {"Btn 16 Mode", m_btn_mode, &amp;MenuValues[47], &amp;setBtnMode, 0, 3},</v>
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">  {"Btn 14 Mode", m_btn_mode, &amp;MenuValues[47], &amp;setBtnMode, 0, 3},</v>
       </c>
       <c r="M49" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  0,  // Btn 16 Mode</v>
+        <v xml:space="preserve">  0,  // Btn 14 Mode</v>
       </c>
       <c r="N49" s="11"/>
     </row>
@@ -3845,46 +3863,47 @@
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="B50" s="13" t="s">
-        <v>175</v>
+      <c r="B50" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="C50" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="D50" s="61">
-        <v>-1</v>
-      </c>
-      <c r="E50" s="61">
-        <v>-1</v>
-      </c>
-      <c r="F50" s="61">
-        <v>-1</v>
-      </c>
-      <c r="G50" s="29" t="s">
-        <v>96</v>
+      <c r="D50" s="20">
+        <v>0</v>
+      </c>
+      <c r="E50" s="20">
+        <v>3</v>
+      </c>
+      <c r="F50" s="20">
+        <v>0</v>
+      </c>
+      <c r="G50" s="29" t="str">
+        <f t="shared" si="22"/>
+        <v>MenuValues[48]</v>
       </c>
       <c r="H50" s="29" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="I50" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Btn Mode", </v>
+        <v xml:space="preserve">"Btn 15 Mode", </v>
       </c>
       <c r="J50" s="44" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">NULL, </v>
+        <v xml:space="preserve">&amp;MenuValues[48], </v>
       </c>
       <c r="K50" s="44" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">NULL, </v>
+        <v xml:space="preserve">&amp;setBtnMode, </v>
       </c>
       <c r="L50" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">  {"Btn Mode", m_btn_mode, NULL, NULL, -1, -1},</v>
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">  {"Btn 15 Mode", m_btn_mode, &amp;MenuValues[48], &amp;setBtnMode, 0, 3},</v>
       </c>
       <c r="M50" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Btn Mode</v>
+        <v xml:space="preserve">  0,  // Btn 15 Mode</v>
       </c>
       <c r="N50" s="11"/>
     </row>
@@ -3893,31 +3912,31 @@
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="B51" s="12" t="s">
-        <v>4</v>
+      <c r="B51" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="D51" s="30">
-        <v>0</v>
-      </c>
-      <c r="E51" s="12">
-        <v>4</v>
-      </c>
-      <c r="F51" s="30">
-        <v>1</v>
+        <v>172</v>
+      </c>
+      <c r="D51" s="20">
+        <v>0</v>
+      </c>
+      <c r="E51" s="20">
+        <v>3</v>
+      </c>
+      <c r="F51" s="20">
+        <v>0</v>
       </c>
       <c r="G51" s="29" t="str">
-        <f>CONCATENATE("MenuValues[",A51,"]")</f>
+        <f t="shared" si="22"/>
         <v>MenuValues[49]</v>
       </c>
       <c r="H51" s="29" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="I51" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Kbd Driver", </v>
+        <v xml:space="preserve">"Btn 16 Mode", </v>
       </c>
       <c r="J51" s="44" t="str">
         <f t="shared" si="3"/>
@@ -3925,15 +3944,15 @@
       </c>
       <c r="K51" s="44" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">&amp;setKbdDriver, </v>
+        <v xml:space="preserve">&amp;setBtnMode, </v>
       </c>
       <c r="L51" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">  {"Kbd Driver", m_kbd_driver, &amp;MenuValues[49], &amp;setKbdDriver, 0, 4},</v>
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">  {"Btn 16 Mode", m_btn_mode, &amp;MenuValues[49], &amp;setBtnMode, 0, 3},</v>
       </c>
       <c r="M51" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  1,  // Kbd Driver</v>
+        <v xml:space="preserve">  0,  // Btn 16 Mode</v>
       </c>
       <c r="N51" s="11"/>
     </row>
@@ -3942,47 +3961,46 @@
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>5</v>
+      <c r="B52" s="13" t="s">
+        <v>175</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="D52" s="20">
-        <v>1</v>
-      </c>
-      <c r="E52" s="1">
-        <v>30</v>
-      </c>
-      <c r="F52" s="20">
-        <v>10</v>
-      </c>
-      <c r="G52" s="29" t="str">
-        <f>CONCATENATE("MenuValues[",A52,"]")</f>
-        <v>MenuValues[50]</v>
-      </c>
-      <c r="H52" s="36" t="s">
-        <v>180</v>
+        <v>172</v>
+      </c>
+      <c r="D52" s="61">
+        <v>-1</v>
+      </c>
+      <c r="E52" s="61">
+        <v>-1</v>
+      </c>
+      <c r="F52" s="61">
+        <v>-1</v>
+      </c>
+      <c r="G52" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="H52" s="29" t="s">
+        <v>96</v>
       </c>
       <c r="I52" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Velocity Min", </v>
+        <v xml:space="preserve">"Btn Mode", </v>
       </c>
       <c r="J52" s="44" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">&amp;MenuValues[50], </v>
+        <v xml:space="preserve">NULL, </v>
       </c>
       <c r="K52" s="44" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">&amp;setDynSlope, </v>
+        <v xml:space="preserve">NULL, </v>
       </c>
       <c r="L52" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">  {"Velocity Min", m_kbd_driver, &amp;MenuValues[50], &amp;setDynSlope, 1, 30},</v>
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">  {"Btn Mode", m_btn_mode, NULL, NULL, -1, -1},</v>
       </c>
       <c r="M52" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  10,  // Velocity Min</v>
+        <v xml:space="preserve">  -1,  // Btn Mode</v>
       </c>
       <c r="N52" s="11"/>
     </row>
@@ -3991,31 +4009,31 @@
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>24</v>
+      <c r="B53" s="12" t="s">
+        <v>4</v>
       </c>
       <c r="C53" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="D53" s="20">
-        <v>0</v>
-      </c>
-      <c r="E53" s="1">
-        <v>20</v>
-      </c>
-      <c r="F53" s="20">
-        <v>10</v>
+      <c r="D53" s="30">
+        <v>0</v>
+      </c>
+      <c r="E53" s="12">
+        <v>4</v>
+      </c>
+      <c r="F53" s="30">
+        <v>1</v>
       </c>
       <c r="G53" s="29" t="str">
         <f>CONCATENATE("MenuValues[",A53,"]")</f>
         <v>MenuValues[51]</v>
       </c>
       <c r="H53" s="29" t="s">
-        <v>96</v>
+        <v>176</v>
       </c>
       <c r="I53" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Velocity MaxAdj", </v>
+        <v xml:space="preserve">"Kbd Driver", </v>
       </c>
       <c r="J53" s="44" t="str">
         <f t="shared" si="3"/>
@@ -4023,15 +4041,15 @@
       </c>
       <c r="K53" s="44" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">NULL, </v>
+        <v xml:space="preserve">&amp;setKbdDriver, </v>
       </c>
       <c r="L53" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">  {"Velocity MaxAdj", m_kbd_driver, &amp;MenuValues[51], NULL, 0, 20},</v>
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">  {"Kbd Driver", m_kbd_driver, &amp;MenuValues[51], &amp;setKbdDriver, 0, 4},</v>
       </c>
       <c r="M53" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  10,  // Velocity MaxAdj</v>
+        <v xml:space="preserve">  1,  // Kbd Driver</v>
       </c>
       <c r="N53" s="11"/>
     </row>
@@ -4041,7 +4059,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C54" s="20" t="s">
         <v>111</v>
@@ -4050,10 +4068,10 @@
         <v>1</v>
       </c>
       <c r="E54" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F54" s="20">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G54" s="29" t="str">
         <f>CONCATENATE("MenuValues[",A54,"]")</f>
@@ -4064,7 +4082,7 @@
       </c>
       <c r="I54" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Velocity Slope", </v>
+        <v xml:space="preserve">"Velocity Min", </v>
       </c>
       <c r="J54" s="44" t="str">
         <f t="shared" si="3"/>
@@ -4075,120 +4093,120 @@
         <v xml:space="preserve">&amp;setDynSlope, </v>
       </c>
       <c r="L54" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">  {"Velocity Slope", m_kbd_driver, &amp;MenuValues[52], &amp;setDynSlope, 1, 40},</v>
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">  {"Velocity Min", m_kbd_driver, &amp;MenuValues[52], &amp;setDynSlope, 1, 30},</v>
       </c>
       <c r="M54" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  20,  // Velocity Slope</v>
+        <v xml:space="preserve">  10,  // Velocity Min</v>
       </c>
       <c r="N54" s="11"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="21">
-        <f t="shared" ref="A55:A58" si="16">A54+1</f>
+        <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C55" s="20" t="s">
         <v>111</v>
       </c>
       <c r="D55" s="20">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F55" s="20">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="G55" s="29" t="str">
-        <f t="shared" ref="G55:G58" si="17">CONCATENATE("MenuValues[",A55,"]")</f>
+        <f>CONCATENATE("MenuValues[",A55,"]")</f>
         <v>MenuValues[53]</v>
       </c>
       <c r="H55" s="29" t="s">
         <v>96</v>
       </c>
       <c r="I55" s="43" t="str">
-        <f t="shared" ref="I55:I58" si="18">CONCATENATE("""",B55,""", ")</f>
-        <v xml:space="preserve">"Upper Base", </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">"Velocity MaxAdj", </v>
       </c>
       <c r="J55" s="44" t="str">
-        <f t="shared" ref="J55:J58" si="19">IF(G55="NULL",CONCATENATE(G55,", "),CONCATENATE("&amp;",G55,", "))</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">&amp;MenuValues[53], </v>
       </c>
       <c r="K55" s="44" t="str">
-        <f t="shared" ref="K55:K58" si="20">IF(H55="NULL",CONCATENATE(H55,", "),CONCATENATE("&amp;",H55,", "))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="L55" s="40" t="str">
-        <f t="shared" ref="L55:L58" si="21">CONCATENATE("  {",I55,C55,", ",J55,K55,D55,", ",E55,"},")</f>
-        <v xml:space="preserve">  {"Upper Base", m_kbd_driver, &amp;MenuValues[53], NULL, 12, 60},</v>
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">  {"Velocity MaxAdj", m_kbd_driver, &amp;MenuValues[53], NULL, 0, 20},</v>
       </c>
       <c r="M55" s="76" t="str">
-        <f t="shared" ref="M55:M58" si="22" xml:space="preserve"> CONCATENATE("  ",F55,",  // ",B55)</f>
-        <v xml:space="preserve">  36,  // Upper Base</v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">  10,  // Velocity MaxAdj</v>
       </c>
       <c r="N55" s="11"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="21">
-        <f t="shared" si="16"/>
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C56" s="20" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="20">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E56" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F56" s="20">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G56" s="29" t="str">
-        <f t="shared" si="17"/>
+        <f>CONCATENATE("MenuValues[",A56,"]")</f>
         <v>MenuValues[54]</v>
       </c>
-      <c r="H56" s="29" t="s">
-        <v>96</v>
+      <c r="H56" s="36" t="s">
+        <v>180</v>
       </c>
       <c r="I56" s="43" t="str">
-        <f t="shared" si="18"/>
-        <v xml:space="preserve">"Lower Base", </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">"Velocity Slope", </v>
       </c>
       <c r="J56" s="44" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">&amp;MenuValues[54], </v>
       </c>
       <c r="K56" s="44" t="str">
-        <f t="shared" si="20"/>
-        <v xml:space="preserve">NULL, </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">&amp;setDynSlope, </v>
       </c>
       <c r="L56" s="40" t="str">
-        <f t="shared" si="21"/>
-        <v xml:space="preserve">  {"Lower Base", m_kbd_driver, &amp;MenuValues[54], NULL, 12, 60},</v>
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">  {"Velocity Slope", m_kbd_driver, &amp;MenuValues[54], &amp;setDynSlope, 1, 40},</v>
       </c>
       <c r="M56" s="76" t="str">
-        <f t="shared" si="22"/>
-        <v xml:space="preserve">  36,  // Lower Base</v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">  20,  // Velocity Slope</v>
       </c>
       <c r="N56" s="11"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="21">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="A57:A60" si="24">A56+1</f>
         <v>55</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C57" s="20" t="s">
         <v>111</v>
@@ -4203,224 +4221,322 @@
         <v>36</v>
       </c>
       <c r="G57" s="29" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="G57:G60" si="25">CONCATENATE("MenuValues[",A57,"]")</f>
         <v>MenuValues[55]</v>
       </c>
       <c r="H57" s="29" t="s">
         <v>96</v>
       </c>
       <c r="I57" s="43" t="str">
-        <f t="shared" si="18"/>
-        <v xml:space="preserve">"Pedal Base", </v>
+        <f t="shared" ref="I57:I60" si="26">CONCATENATE("""",B57,""", ")</f>
+        <v xml:space="preserve">"Upper Base", </v>
       </c>
       <c r="J57" s="44" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="J57:J60" si="27">IF(G57="NULL",CONCATENATE(G57,", "),CONCATENATE("&amp;",G57,", "))</f>
         <v xml:space="preserve">&amp;MenuValues[55], </v>
       </c>
       <c r="K57" s="44" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="K57:K60" si="28">IF(H57="NULL",CONCATENATE(H57,", "),CONCATENATE("&amp;",H57,", "))</f>
         <v xml:space="preserve">NULL, </v>
       </c>
       <c r="L57" s="40" t="str">
-        <f t="shared" si="21"/>
-        <v xml:space="preserve">  {"Pedal Base", m_kbd_driver, &amp;MenuValues[55], NULL, 12, 60},</v>
+        <f t="shared" ref="L57:L60" si="29">CONCATENATE("  {",I57,C57,", ",J57,K57,D57,", ",E57,"},")</f>
+        <v xml:space="preserve">  {"Upper Base", m_kbd_driver, &amp;MenuValues[55], NULL, 12, 60},</v>
       </c>
       <c r="M57" s="76" t="str">
-        <f t="shared" si="22"/>
-        <v xml:space="preserve">  36,  // Pedal Base</v>
-      </c>
+        <f t="shared" ref="M57:M60" si="30" xml:space="preserve"> CONCATENATE("  ",F57,",  // ",B57)</f>
+        <v xml:space="preserve">  36,  // Upper Base</v>
+      </c>
+      <c r="N57" s="11"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="21">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>56</v>
       </c>
-      <c r="B58" s="13" t="s">
-        <v>25</v>
+      <c r="B58" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C58" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="D58" s="61">
-        <v>-1</v>
-      </c>
-      <c r="E58" s="61">
-        <v>-1</v>
-      </c>
-      <c r="F58" s="61">
-        <v>-1</v>
+      <c r="D58" s="20">
+        <v>12</v>
+      </c>
+      <c r="E58" s="1">
+        <v>60</v>
+      </c>
+      <c r="F58" s="20">
+        <v>36</v>
       </c>
       <c r="G58" s="29" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>MenuValues[56]</v>
       </c>
       <c r="H58" s="29" t="s">
         <v>96</v>
       </c>
       <c r="I58" s="43" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">"Lower Base", </v>
+      </c>
+      <c r="J58" s="44" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">&amp;MenuValues[56], </v>
+      </c>
+      <c r="K58" s="44" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="L58" s="40" t="str">
+        <f t="shared" si="29"/>
+        <v xml:space="preserve">  {"Lower Base", m_kbd_driver, &amp;MenuValues[56], NULL, 12, 60},</v>
+      </c>
+      <c r="M58" s="76" t="str">
+        <f t="shared" si="30"/>
+        <v xml:space="preserve">  36,  // Lower Base</v>
+      </c>
+      <c r="N58" s="11"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59" s="21">
+        <f t="shared" si="24"/>
+        <v>57</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="D59" s="20">
+        <v>12</v>
+      </c>
+      <c r="E59" s="1">
+        <v>60</v>
+      </c>
+      <c r="F59" s="20">
+        <v>36</v>
+      </c>
+      <c r="G59" s="29" t="str">
+        <f t="shared" si="25"/>
+        <v>MenuValues[57]</v>
+      </c>
+      <c r="H59" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="I59" s="43" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">"Pedal Base", </v>
+      </c>
+      <c r="J59" s="44" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">&amp;MenuValues[57], </v>
+      </c>
+      <c r="K59" s="44" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="L59" s="40" t="str">
+        <f t="shared" si="29"/>
+        <v xml:space="preserve">  {"Pedal Base", m_kbd_driver, &amp;MenuValues[57], NULL, 12, 60},</v>
+      </c>
+      <c r="M59" s="76" t="str">
+        <f t="shared" si="30"/>
+        <v xml:space="preserve">  36,  // Pedal Base</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" s="21">
+        <f t="shared" si="24"/>
+        <v>58</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C60" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="D60" s="61">
+        <v>-1</v>
+      </c>
+      <c r="E60" s="61">
+        <v>-1</v>
+      </c>
+      <c r="F60" s="61">
+        <v>-1</v>
+      </c>
+      <c r="G60" s="29" t="str">
+        <f t="shared" si="25"/>
+        <v>MenuValues[58]</v>
+      </c>
+      <c r="H60" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="I60" s="43" t="str">
+        <f t="shared" si="26"/>
         <v xml:space="preserve">"Keyboard", </v>
       </c>
-      <c r="J58" s="44" t="str">
-        <f t="shared" si="19"/>
-        <v xml:space="preserve">&amp;MenuValues[56], </v>
-      </c>
-      <c r="K58" s="44" t="str">
-        <f t="shared" si="20"/>
-        <v xml:space="preserve">NULL, </v>
-      </c>
-      <c r="L58" s="40" t="str">
-        <f t="shared" si="21"/>
-        <v xml:space="preserve">  {"Keyboard", m_kbd_driver, &amp;MenuValues[56], NULL, -1, -1},</v>
-      </c>
-      <c r="M58" s="76" t="str">
-        <f t="shared" si="22"/>
+      <c r="J60" s="44" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">&amp;MenuValues[58], </v>
+      </c>
+      <c r="K60" s="44" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">NULL, </v>
+      </c>
+      <c r="L60" s="40" t="str">
+        <f t="shared" si="29"/>
+        <v xml:space="preserve">  {"Keyboard", m_kbd_driver, &amp;MenuValues[58], NULL, -1, -1},</v>
+      </c>
+      <c r="M60" s="76" t="str">
+        <f t="shared" si="30"/>
         <v xml:space="preserve">  -1,  // Keyboard</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="77">
-        <f>A58+1</f>
-        <v>57</v>
-      </c>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="9" t="s">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61" s="77">
+        <f>A60+1</f>
+        <v>59</v>
+      </c>
+      <c r="G61" s="20"/>
+      <c r="H61" s="20"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="K59" s="1" t="s">
+      <c r="K61" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L59" s="40" t="s">
+      <c r="L61" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="M59" s="39" t="s">
+      <c r="M61" s="39" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="73" t="s">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" s="73" t="s">
         <v>163</v>
       </c>
-      <c r="B60" s="20" t="s">
+      <c r="B62" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="C60" s="68" t="s">
+      <c r="C62" s="68" t="s">
         <v>161</v>
       </c>
-      <c r="D60" s="61">
-        <v>-1</v>
-      </c>
-      <c r="E60" s="61">
-        <v>-1</v>
-      </c>
-      <c r="F60" s="61"/>
-      <c r="G60" s="19" t="s">
+      <c r="D62" s="61">
+        <v>-1</v>
+      </c>
+      <c r="E62" s="61">
+        <v>-1</v>
+      </c>
+      <c r="F62" s="61"/>
+      <c r="G62" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="J60" s="10"/>
-      <c r="L60" s="40" t="s">
+      <c r="J62" s="10"/>
+      <c r="L62" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="M60" s="76"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="73" t="s">
+      <c r="M62" s="76"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" s="73" t="s">
         <v>163</v>
       </c>
-      <c r="B61" s="20" t="s">
+      <c r="B63" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="C61" s="68" t="s">
+      <c r="C63" s="68" t="s">
         <v>161</v>
       </c>
-      <c r="D61" s="70">
-        <v>0</v>
-      </c>
-      <c r="E61" s="70">
-        <v>0</v>
-      </c>
-      <c r="F61" s="70"/>
-      <c r="G61" s="19" t="s">
+      <c r="D63" s="70">
+        <v>0</v>
+      </c>
+      <c r="E63" s="70">
+        <v>0</v>
+      </c>
+      <c r="F63" s="70"/>
+      <c r="G63" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="L61" s="74" t="str">
-        <f>CONCATENATE("#define MENU_POT_CC ",A12)</f>
-        <v>#define MENU_POT_CC 10</v>
-      </c>
-      <c r="M61" s="76"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G62" s="39" t="str">
-        <f>CONCATENATE("#define MENU_ITEMCOUNT ",A59)</f>
-        <v>#define MENU_ITEMCOUNT 57</v>
-      </c>
-      <c r="H62" s="39"/>
-      <c r="I62" s="6" t="s">
+      <c r="L63" s="74" t="str">
+        <f>CONCATENATE("#define MENU_POT_CC ",A14)</f>
+        <v>#define MENU_POT_CC 12</v>
+      </c>
+      <c r="M63" s="76"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G64" s="39" t="str">
+        <f>CONCATENATE("#define MENU_ITEMCOUNT ",A61)</f>
+        <v>#define MENU_ITEMCOUNT 59</v>
+      </c>
+      <c r="H64" s="39"/>
+      <c r="I64" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="L62" s="74" t="str">
-        <f>CONCATENATE("#define MENU_BTN_CC ",A17)</f>
-        <v>#define MENU_BTN_CC 15</v>
-      </c>
-      <c r="M62" s="76"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="L63" s="74" t="str">
-        <f>CONCATENATE("#define MENU_BTN_MODE ",A34)</f>
-        <v>#define MENU_BTN_MODE 32</v>
-      </c>
-      <c r="M63" s="76"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="L64" s="74" t="str">
-        <f>CONCATENATE("#define MENU_KBD_DRIVER ",A51)</f>
-        <v>#define MENU_KBD_DRIVER 49</v>
+        <f>CONCATENATE("#define MENU_BTN_CC ",A19)</f>
+        <v>#define MENU_BTN_CC 17</v>
       </c>
       <c r="M64" s="76"/>
     </row>
     <row r="65" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L65" s="74" t="str">
-        <f>CONCATENATE("#define MENU_MIN_DYN ",A52)</f>
-        <v>#define MENU_MIN_DYN 50</v>
+        <f>CONCATENATE("#define MENU_BTN_MODE ",A36)</f>
+        <v>#define MENU_BTN_MODE 34</v>
       </c>
       <c r="M65" s="76"/>
     </row>
     <row r="66" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L66" s="74" t="str">
-        <f>CONCATENATE("#define MENU_MAX_DYNADJ ",A53)</f>
-        <v>#define MENU_MAX_DYNADJ 51</v>
+        <f>CONCATENATE("#define MENU_KBD_DRIVER ",A53)</f>
+        <v>#define MENU_KBD_DRIVER 51</v>
       </c>
       <c r="M66" s="76"/>
     </row>
     <row r="67" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L67" s="74" t="str">
-        <f>CONCATENATE("#define MENU_DYNSLOPE ",A54)</f>
-        <v>#define MENU_DYNSLOPE 52</v>
+        <f>CONCATENATE("#define MENU_MIN_DYN ",A54)</f>
+        <v>#define MENU_MIN_DYN 52</v>
       </c>
       <c r="M67" s="76"/>
     </row>
     <row r="68" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L68" s="74" t="str">
-        <f>CONCATENATE("#define MENU_BASE_UPR ",A55)</f>
-        <v>#define MENU_BASE_UPR 53</v>
+        <f>CONCATENATE("#define MENU_MAX_DYNADJ ",A55)</f>
+        <v>#define MENU_MAX_DYNADJ 53</v>
       </c>
       <c r="M68" s="76"/>
     </row>
     <row r="69" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L69" s="74" t="str">
-        <f>CONCATENATE("#define MENU_BASE_LWR ",A56)</f>
-        <v>#define MENU_BASE_LWR 54</v>
+        <f>CONCATENATE("#define MENU_DYNSLOPE ",A56)</f>
+        <v>#define MENU_DYNSLOPE 54</v>
       </c>
       <c r="M69" s="76"/>
     </row>
     <row r="70" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L70" s="74" t="str">
-        <f>CONCATENATE("#define MENU_BASE_PED ",A57)</f>
-        <v>#define MENU_BASE_PED 55</v>
+        <f>CONCATENATE("#define MENU_BASE_UPR ",A57)</f>
+        <v>#define MENU_BASE_UPR 55</v>
       </c>
       <c r="M70" s="76"/>
+    </row>
+    <row r="71" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L71" s="74" t="str">
+        <f>CONCATENATE("#define MENU_BASE_LWR ",A58)</f>
+        <v>#define MENU_BASE_LWR 56</v>
+      </c>
+      <c r="M71" s="76"/>
+    </row>
+    <row r="72" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L72" s="74" t="str">
+        <f>CONCATENATE("#define MENU_BASE_PED ",A59)</f>
+        <v>#define MENU_BASE_PED 57</v>
+      </c>
+      <c r="M72" s="76"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/docs/MIDI_menuItems.xlsx
+++ b/docs/MIDI_menuItems.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="189">
   <si>
     <t>Index #</t>
   </si>
@@ -584,6 +584,9 @@
   </si>
   <si>
     <t>Swell CC</t>
+  </si>
+  <si>
+    <t>Pitchwhl Pot#</t>
   </si>
 </sst>
 </file>
@@ -1692,7 +1695,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>59</v>
+        <v>188</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>157</v>
@@ -1715,7 +1718,7 @@
       </c>
       <c r="I6" s="43" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">"Pitchwheel Pot", </v>
+        <v xml:space="preserve">"Pitchwhl Pot#", </v>
       </c>
       <c r="J6" s="44" t="str">
         <f t="shared" si="3"/>
@@ -1727,11 +1730,11 @@
       </c>
       <c r="L6" s="40" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">  {"Pitchwheel Pot", m_pitchwheel, &amp;MenuValues[4], NULL, -1, 15},</v>
+        <v xml:space="preserve">  {"Pitchwhl Pot#", m_pitchwheel, &amp;MenuValues[4], NULL, -1, 15},</v>
       </c>
       <c r="M6" s="76" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">  -1,  // Pitchwheel Pot</v>
+        <v xml:space="preserve">  -1,  // Pitchwhl Pot#</v>
       </c>
       <c r="N6" s="53" t="str">
         <f t="shared" ref="N6:N13" si="13">CONCATENATE("  ",C6,",")</f>
